--- a/data/trans_orig/dukeCONF-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/dukeCONF-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala de apoyo confidencial (Duke)</t>
+          <t>Puntuación media de la escala de apoyo confidencial (Duke) (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,26; 28,99</t>
+          <t>28,19; 28,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,33; 30,08</t>
+          <t>29,3; 30,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,64; 29,38</t>
+          <t>28,57; 29,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,13; 29,21</t>
+          <t>28,19; 29,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,6; 28,26</t>
+          <t>27,55; 28,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,06; 29,64</t>
+          <t>29,04; 29,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,81; 28,55</t>
+          <t>27,85; 28,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,93; 28,67</t>
+          <t>27,94; 28,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,99; 28,49</t>
+          <t>27,99; 28,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,26; 29,71</t>
+          <t>29,25; 29,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,29; 28,82</t>
+          <t>28,28; 28,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,18; 28,79</t>
+          <t>28,18; 28,78</t>
         </is>
       </c>
     </row>
@@ -856,42 +856,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,45; 30,93</t>
+          <t>30,47; 30,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,63; 31,05</t>
+          <t>30,62; 31,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,41; 29,83</t>
+          <t>29,42; 29,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,78; 32,46</t>
+          <t>30,74; 32,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,84; 30,37</t>
+          <t>29,85; 30,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,92; 30,41</t>
+          <t>29,92; 30,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,49; 29,87</t>
+          <t>29,46; 29,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,48; 31,3</t>
+          <t>30,48; 31,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,73; 31,79</t>
+          <t>30,74; 31,81</t>
         </is>
       </c>
     </row>
@@ -996,32 +996,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,34; 31,21</t>
+          <t>30,3; 31,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,8; 31,73</t>
+          <t>30,82; 31,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,42; 31,12</t>
+          <t>30,39; 31,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,02; 31,88</t>
+          <t>30,96; 31,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,23; 31,18</t>
+          <t>30,22; 31,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,1; 31,89</t>
+          <t>31,14; 31,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,55; 32,12</t>
+          <t>31,58; 32,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31,12; 31,76</t>
+          <t>31,13; 31,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,51; 31,04</t>
+          <t>30,55; 31,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,41; 31,91</t>
+          <t>31,4; 31,92</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,87; 30,23</t>
+          <t>29,87; 30,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,42; 30,76</t>
+          <t>30,41; 30,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,52; 29,84</t>
+          <t>29,5; 29,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,56; 31,96</t>
+          <t>30,58; 31,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,14; 29,52</t>
+          <t>29,16; 29,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,87; 30,2</t>
+          <t>29,86; 30,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,28; 29,62</t>
+          <t>29,27; 29,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,25; 30,78</t>
+          <t>30,22; 30,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,57; 29,83</t>
+          <t>29,56; 29,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,19; 30,43</t>
+          <t>30,18; 30,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,44; 29,66</t>
+          <t>29,45; 29,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,45; 31,28</t>
+          <t>30,47; 31,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/dukeCONF-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/dukeCONF-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28,73</t>
+          <t>28,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,29</t>
+          <t>28,17</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,47</t>
+          <t>28,34</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,19; 28,95</t>
+          <t>28,25; 28,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,3; 30,05</t>
+          <t>29,33; 30,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,57; 29,32</t>
+          <t>28,57; 29,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,19; 29,24</t>
+          <t>28,01; 29,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,55; 28,23</t>
+          <t>27,56; 28,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,04; 29,64</t>
+          <t>29,06; 29,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,85; 28,58</t>
+          <t>27,86; 28,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,94; 28,66</t>
+          <t>27,83; 28,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,99; 28,48</t>
+          <t>27,96; 28,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,25; 29,71</t>
+          <t>29,27; 29,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,28; 28,81</t>
+          <t>28,29; 28,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,18; 28,78</t>
+          <t>28,04; 28,65</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31,29</t>
+          <t>30,65</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,76</t>
+          <t>30,41</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,04</t>
+          <t>30,53</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,47; 30,93</t>
+          <t>30,46; 30,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,62; 31,07</t>
+          <t>30,62; 31,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,42; 29,84</t>
+          <t>29,43; 29,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,74; 32,59</t>
+          <t>30,4; 30,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,85; 30,35</t>
+          <t>29,84; 30,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,92; 30,38</t>
+          <t>29,92; 30,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,46; 29,87</t>
+          <t>29,47; 29,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,48; 31,22</t>
+          <t>30,16; 30,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,23; 30,58</t>
+          <t>30,24; 30,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,37; 30,69</t>
+          <t>30,36; 30,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,52; 29,79</t>
+          <t>29,51; 29,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,74; 31,81</t>
+          <t>30,36; 30,69</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31,47</t>
+          <t>31,45</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31,87</t>
+          <t>31,81</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,67</t>
+          <t>31,63</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,3; 31,17</t>
+          <t>30,3; 31,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,82; 31,75</t>
+          <t>30,82; 31,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,39; 31,12</t>
+          <t>30,44; 31,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,96; 31,86</t>
+          <t>30,99; 31,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,22; 31,1</t>
+          <t>30,24; 31,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,14; 31,86</t>
+          <t>31,14; 31,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,43; 31,11</t>
+          <t>30,4; 31,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,58; 32,12</t>
+          <t>31,5; 32,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,43; 31,06</t>
+          <t>30,43; 31,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31,13; 31,73</t>
+          <t>31,15; 31,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,55; 31,03</t>
+          <t>30,51; 31,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,4; 31,92</t>
+          <t>31,38; 31,85</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30,94</t>
+          <t>30,47</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,44</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,69</t>
+          <t>30,33</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,87; 30,25</t>
+          <t>29,88; 30,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,41; 30,76</t>
+          <t>30,4; 30,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,32 +1151,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,58; 31,86</t>
+          <t>30,28; 30,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,16; 29,53</t>
+          <t>29,14; 29,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,86; 30,22</t>
+          <t>29,87; 30,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,27; 29,62</t>
+          <t>29,28; 29,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,22; 30,76</t>
+          <t>30,03; 30,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,56; 29,83</t>
+          <t>29,55; 29,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,45; 29,68</t>
+          <t>29,45; 29,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,47; 31,17</t>
+          <t>30,21; 30,47</t>
         </is>
       </c>
     </row>
